--- a/demo_data/interlock/DEMO_INTERLOCK_LIST.xlsx
+++ b/demo_data/interlock/DEMO_INTERLOCK_LIST.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N95"/>
+  <dimension ref="A1:N106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>LIT-4003 Low Low (10 %) 5sec (탱크 저수위)</t>
+          <t>MOTOR OVERLOAD TRIP (49)</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>탱크 저수위 연동. 캐비테이션 방지. * Valve Action : Fail Stop</t>
+          <t>기기 고장 보호. 래치되며 인터락 리셋으로만 해제. * Valve Action : Fail Stop</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>PIT-5004 Low Low &lt; 0.9 bar 5sec</t>
+          <t>E-STOP PB 동작</t>
         </is>
       </c>
       <c r="H62" s="3" t="n"/>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>MOTOR OVERLOAD TRIP (49)</t>
+          <t>VFD FAULT 발생</t>
         </is>
       </c>
       <c r="H63" s="3" t="n"/>
@@ -3013,11 +3013,31 @@
       <c r="N63" s="3" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n"/>
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="3" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="3" t="n"/>
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>IL-5101A-02</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>P-5101A</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>PERMISSIVE</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -3025,43 +3045,49 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>E-STOP PB 동작</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="n"/>
-      <c r="I64" s="3" t="n"/>
-      <c r="J64" s="3" t="n"/>
-      <c r="K64" s="3" t="n"/>
-      <c r="L64" s="3" t="n"/>
-      <c r="M64" s="3" t="n"/>
-      <c r="N64" s="3" t="n"/>
+          <t>LIT-4003 &gt; 25 %</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>FB_P5101A_PERM</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>YI-Y01-C01-UW-LG-051</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>* Valve Action : Fail Stop</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>IL-5101A-02</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>P-5101A</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>START</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>PERMISSIVE</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
+      <c r="A65" s="3" t="n"/>
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n"/>
       <c r="F65" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -3069,42 +3095,16 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>LIT-4003 &gt; 25 %</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J65" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>FB_P5101A_PERM</t>
-        </is>
-      </c>
-      <c r="L65" s="3" t="inlineStr">
-        <is>
-          <t>YI-Y01-C01-UW-LG-051</t>
-        </is>
-      </c>
-      <c r="M65" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N65" s="3" t="inlineStr">
-        <is>
-          <t>* Valve Action : Fail Stop</t>
-        </is>
-      </c>
+          <t>XV-5103 OPEN 확인</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="n"/>
+      <c r="I65" s="3" t="n"/>
+      <c r="J65" s="3" t="n"/>
+      <c r="K65" s="3" t="n"/>
+      <c r="L65" s="3" t="n"/>
+      <c r="M65" s="3" t="n"/>
+      <c r="N65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n"/>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>XV-5103 OPEN 확인</t>
+          <t>MCC READY 신호 정상</t>
         </is>
       </c>
       <c r="H66" s="3" t="n"/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>MCC READY 신호 정상</t>
+          <t>VFD FAULT 없음</t>
         </is>
       </c>
       <c r="H67" s="3" t="n"/>
@@ -3155,11 +3155,31 @@
       <c r="N67" s="3" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n"/>
-      <c r="B68" s="3" t="n"/>
-      <c r="C68" s="3" t="n"/>
-      <c r="D68" s="3" t="n"/>
-      <c r="E68" s="3" t="n"/>
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>IL-5101A-03</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>P-5101A</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>SEQUENCE</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -3167,110 +3187,136 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>VFD FAULT 없음</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="n"/>
-      <c r="I68" s="3" t="n"/>
-      <c r="J68" s="3" t="n"/>
-      <c r="K68" s="3" t="n"/>
-      <c r="L68" s="3" t="n"/>
-      <c r="M68" s="3" t="n"/>
-      <c r="N68" s="3" t="n"/>
+          <t>LIT-4003 Low Low (10 %) 5sec (탱크 저수위)</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>SFC_P5101A_AUTO</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>YI-Y01-C01-UW-LG-051</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>자동 운전 정지. 원인 해소 시 자동 재기동. 래치 없음. * Valve Action : Fail Stop</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>IL-5102-01</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>UV-5102</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="A69" s="3" t="n"/>
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n"/>
+      <c r="D69" s="3" t="n"/>
+      <c r="E69" s="3" t="n"/>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>XV-5103 CLOSE 확인 3sec (토출 밸브 폐쇄, 체절운전 방지)</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="n"/>
+      <c r="I69" s="3" t="n"/>
+      <c r="J69" s="3" t="n"/>
+      <c r="K69" s="3" t="n"/>
+      <c r="L69" s="3" t="n"/>
+      <c r="M69" s="3" t="n"/>
+      <c r="N69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>IL-5101B-01</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>P-5101B</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>INTERLOCK</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>P-5101A 및 P-5101B 모두 정지 (무통수)</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>MOTOR OVERLOAD TRIP (49)</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J69" s="3" t="n">
+      <c r="J70" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>FB_UV5102_ILK</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>FB_P5101B_ILK</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
         <is>
           <t>YI-Y01-C01-UW-LG-051</t>
         </is>
       </c>
-      <c r="M69" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N69" s="3" t="inlineStr">
-        <is>
-          <t>무통수 시 UV 점등 금지 — 관내 승온. * Valve Action : Fail Off</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="n"/>
-      <c r="B70" s="3" t="n"/>
-      <c r="C70" s="3" t="n"/>
-      <c r="D70" s="4" t="n"/>
-      <c r="E70" s="3" t="n"/>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>TIT-5005 High High &gt; 60 degC</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="n"/>
-      <c r="I70" s="3" t="n"/>
-      <c r="J70" s="3" t="n"/>
-      <c r="K70" s="3" t="n"/>
-      <c r="L70" s="3" t="n"/>
-      <c r="M70" s="3" t="n"/>
-      <c r="N70" s="3" t="n"/>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
+          <t>기기 고장 보호. 래치되며 인터락 리셋으로만 해제. A호기와 동일 조건. * Valve Action : Fail Stop</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n"/>
@@ -3285,7 +3331,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>UV 램프 FAULT 신호</t>
+          <t>E-STOP PB 동작</t>
         </is>
       </c>
       <c r="H71" s="3" t="n"/>
@@ -3297,125 +3343,105 @@
       <c r="N71" s="3" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>IL-5102-02</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>UV-5102</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="A72" s="3" t="n"/>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>VFD FAULT 발생</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="n"/>
+      <c r="I72" s="3" t="n"/>
+      <c r="J72" s="3" t="n"/>
+      <c r="K72" s="3" t="n"/>
+      <c r="L72" s="3" t="n"/>
+      <c r="M72" s="3" t="n"/>
+      <c r="N72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>IL-5101B-02</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>P-5101B</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>PERMISSIVE</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>AND</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>P-5101A 또는 P-5101B 운전 중</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>LIT-4003 &gt; 25 %</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="I72" s="3" t="inlineStr">
+      <c r="I73" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J72" s="3" t="n">
+      <c r="J73" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K72" s="3" t="inlineStr">
-        <is>
-          <t>FB_UV5102_PERM</t>
-        </is>
-      </c>
-      <c r="L72" s="3" t="inlineStr">
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>FB_P5101B_PERM</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
         <is>
           <t>YI-Y01-C01-UW-LG-051</t>
         </is>
       </c>
-      <c r="M72" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N72" s="3" t="inlineStr">
-        <is>
-          <t>* Valve Action : Fail Off</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="n"/>
-      <c r="B73" s="3" t="n"/>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="n"/>
-      <c r="E73" s="3" t="n"/>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>FIT-5006 &gt;= 5 m3/h 연속 20초</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="n"/>
-      <c r="I73" s="3" t="n"/>
-      <c r="J73" s="3" t="n"/>
-      <c r="K73" s="3" t="n"/>
-      <c r="L73" s="3" t="n"/>
-      <c r="M73" s="3" t="n"/>
-      <c r="N73" s="3" t="n"/>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
+          <t>예비 펌프. A호기 정지 시에만 기동. * Valve Action : Fail Stop</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>IL-5103-01</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>XV-5103</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>INTERLOCK</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>OR</t>
-        </is>
-      </c>
+      <c r="A74" s="3" t="n"/>
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n"/>
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="3" t="n"/>
       <c r="F74" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -3423,48 +3449,22 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>AIT-5001 저항률 &lt; 17 Mohm-cm 30sec</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J74" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>FB_XV5103_ILK</t>
-        </is>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>YI-Y01-C01-UW-LG-051</t>
-        </is>
-      </c>
-      <c r="M74" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N74" s="3" t="inlineStr">
-        <is>
-          <t>* Valve Action : Fail Close</t>
-        </is>
-      </c>
+          <t>XV-5103 OPEN 확인</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="n"/>
+      <c r="I74" s="3" t="n"/>
+      <c r="J74" s="3" t="n"/>
+      <c r="K74" s="3" t="n"/>
+      <c r="L74" s="3" t="n"/>
+      <c r="M74" s="3" t="n"/>
+      <c r="N74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n"/>
       <c r="B75" s="3" t="n"/>
       <c r="C75" s="3" t="n"/>
-      <c r="D75" s="4" t="n"/>
+      <c r="D75" s="3" t="n"/>
       <c r="E75" s="3" t="n"/>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>AIT-5003 TOC &gt; 5 ppb 30sec</t>
+          <t>MCC READY 신호 정상</t>
         </is>
       </c>
       <c r="H75" s="3" t="n"/>
@@ -3488,7 +3488,7 @@
       <c r="A76" s="3" t="n"/>
       <c r="B76" s="3" t="n"/>
       <c r="C76" s="3" t="n"/>
-      <c r="D76" s="4" t="n"/>
+      <c r="D76" s="3" t="n"/>
       <c r="E76" s="3" t="n"/>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>E-STOP PB 동작</t>
+          <t>VFD FAULT 없음</t>
         </is>
       </c>
       <c r="H76" s="3" t="n"/>
@@ -3509,31 +3509,11 @@
       <c r="N76" s="3" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>IL-5103-02</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>XV-5103</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>PERMISSIVE</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>AND</t>
-        </is>
-      </c>
+      <c r="A77" s="3" t="n"/>
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3" t="n"/>
+      <c r="D77" s="3" t="n"/>
+      <c r="E77" s="3" t="n"/>
       <c r="F77" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -3541,160 +3521,180 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>LIT-4003 &gt; 25 %</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
+          <t>P-5101A 정지 상태 (교대 운전)</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="n"/>
+      <c r="I77" s="3" t="n"/>
+      <c r="J77" s="3" t="n"/>
+      <c r="K77" s="3" t="n"/>
+      <c r="L77" s="3" t="n"/>
+      <c r="M77" s="3" t="n"/>
+      <c r="N77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>IL-5101B-03</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>P-5101B</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>SEQUENCE</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>LIT-4003 Low Low (10 %) 5sec (탱크 저수위)</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>AUTO</t>
         </is>
       </c>
-      <c r="I77" s="3" t="inlineStr">
+      <c r="I78" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J77" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t>FB_XV5103_PERM</t>
-        </is>
-      </c>
-      <c r="L77" s="3" t="inlineStr">
+      <c r="J78" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>SFC_P5101B_AUTO</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
         <is>
           <t>YI-Y01-C01-UW-LG-051</t>
         </is>
       </c>
-      <c r="M77" s="3" t="inlineStr">
+      <c r="M78" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N77" s="3" t="inlineStr">
-        <is>
-          <t>* Valve Action : Fail Close</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="n"/>
-      <c r="B78" s="3" t="n"/>
-      <c r="C78" s="3" t="n"/>
-      <c r="D78" s="3" t="n"/>
-      <c r="E78" s="3" t="n"/>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t>AIT-4001 &gt;= 17 Mohm-cm</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="n"/>
-      <c r="I78" s="3" t="n"/>
-      <c r="J78" s="3" t="n"/>
-      <c r="K78" s="3" t="n"/>
-      <c r="L78" s="3" t="n"/>
-      <c r="M78" s="3" t="n"/>
-      <c r="N78" s="3" t="n"/>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>자동 운전 정지. 원인 해소 시 자동 재기동. 래치 없음. * Valve Action : Fail Stop</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>IL-6101A-01</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>P-6101A</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>STOP</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="A79" s="3" t="n"/>
+      <c r="B79" s="3" t="n"/>
+      <c r="C79" s="3" t="n"/>
+      <c r="D79" s="3" t="n"/>
+      <c r="E79" s="3" t="n"/>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>XV-5103 CLOSE 확인 3sec (토출 밸브 폐쇄, 체절운전 방지)</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="n"/>
+      <c r="I79" s="3" t="n"/>
+      <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="n"/>
+      <c r="L79" s="3" t="n"/>
+      <c r="M79" s="3" t="n"/>
+      <c r="N79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>IL-5102-01</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>UV-5102</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
         <is>
           <t>INTERLOCK</t>
         </is>
       </c>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="E80" s="3" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>LIT-4003 Low Low (10 %)</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>P-5101A 및 P-5101B 모두 정지 (무통수)</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
       </c>
-      <c r="I79" s="3" t="inlineStr">
+      <c r="I80" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J79" s="3" t="n">
+      <c r="J80" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K79" s="3" t="inlineStr">
-        <is>
-          <t>FB_P6101A_ILK</t>
-        </is>
-      </c>
-      <c r="L79" s="3" t="inlineStr">
-        <is>
-          <t>YI-Y01-C01-UW-LG-061</t>
-        </is>
-      </c>
-      <c r="M79" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N79" s="3" t="inlineStr">
-        <is>
-          <t>* Valve Action : Fail Stop</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="n"/>
-      <c r="B80" s="3" t="n"/>
-      <c r="C80" s="3" t="n"/>
-      <c r="D80" s="4" t="n"/>
-      <c r="E80" s="3" t="n"/>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>PIT-6003 Low Low &lt; 1.5 bar 5sec</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="n"/>
-      <c r="I80" s="3" t="n"/>
-      <c r="J80" s="3" t="n"/>
-      <c r="K80" s="3" t="n"/>
-      <c r="L80" s="3" t="n"/>
-      <c r="M80" s="3" t="n"/>
-      <c r="N80" s="3" t="n"/>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>FB_UV5102_ILK</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>YI-Y01-C01-UW-LG-051</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
+          <t>무통수 시 UV 점등 금지 — 관내 승온. * Valve Action : Fail Off</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n"/>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>MOTOR OVERLOAD TRIP (49)</t>
+          <t>TIT-5005 High High &gt; 60 degC</t>
         </is>
       </c>
       <c r="H81" s="3" t="n"/>
@@ -3721,31 +3721,11 @@
       <c r="N81" s="3" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>IL-6102-01</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>XV-6102</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>INTERLOCK</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>OR</t>
-        </is>
-      </c>
+      <c r="A82" s="3" t="n"/>
+      <c r="B82" s="3" t="n"/>
+      <c r="C82" s="3" t="n"/>
+      <c r="D82" s="4" t="n"/>
+      <c r="E82" s="3" t="n"/>
       <c r="F82" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -3753,72 +3733,92 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>AIT-6002 저항률 &lt; 17 Mohm-cm 30sec</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="I82" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J82" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K82" s="3" t="inlineStr">
-        <is>
-          <t>FB_XV6102_ILK</t>
-        </is>
-      </c>
-      <c r="L82" s="3" t="inlineStr">
-        <is>
-          <t>YI-Y01-C01-UW-LG-061</t>
-        </is>
-      </c>
-      <c r="M82" s="3" t="inlineStr">
+          <t>UV 램프 FAULT 신호</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="n"/>
+      <c r="I82" s="3" t="n"/>
+      <c r="J82" s="3" t="n"/>
+      <c r="K82" s="3" t="n"/>
+      <c r="L82" s="3" t="n"/>
+      <c r="M82" s="3" t="n"/>
+      <c r="N82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>IL-5102-02</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>UV-5102</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>PERMISSIVE</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>P-5101A 또는 P-5101B 운전 중</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>FB_UV5102_PERM</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>YI-Y01-C01-UW-LG-051</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N82" s="3" t="inlineStr">
-        <is>
-          <t>POU 공급 차단. FAB 직결이라 최우선. * Valve Action : Fail Close</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="n"/>
-      <c r="B83" s="3" t="n"/>
-      <c r="C83" s="3" t="n"/>
-      <c r="D83" s="4" t="n"/>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>AIT-6004 TOC High High &gt; 5 ppb</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="n"/>
-      <c r="I83" s="3" t="n"/>
-      <c r="J83" s="3" t="n"/>
-      <c r="K83" s="3" t="n"/>
-      <c r="L83" s="3" t="n"/>
-      <c r="M83" s="3" t="n"/>
-      <c r="N83" s="3" t="n"/>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
+          <t>* Valve Action : Fail Off</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n"/>
       <c r="B84" s="3" t="n"/>
       <c r="C84" s="3" t="n"/>
-      <c r="D84" s="4" t="n"/>
+      <c r="D84" s="3" t="n"/>
       <c r="E84" s="3" t="n"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>E-STOP PB 동작</t>
+          <t>FIT-5006 &gt;= 5 m3/h 연속 20초</t>
         </is>
       </c>
       <c r="H84" s="3" t="n"/>
@@ -3841,27 +3841,27 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>IL-6102-02</t>
+          <t>IL-5103-01</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>XV-6102</t>
+          <t>XV-5103</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>PERMISSIVE</t>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>INTERLOCK</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>AND</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>P-6101A 운전 중</t>
+          <t>AIT-5001 저항률 &lt; 17 Mohm-cm 30sec</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -3885,26 +3885,26 @@
         </is>
       </c>
       <c r="J85" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>FB_XV6102_PERM</t>
+          <t>FB_XV5103_ILK</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>YI-Y01-C01-UW-LG-061</t>
+          <t>YI-Y01-C01-UW-LG-051</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>바이패스 불가 — 품질 직결. * Valve Action : Fail Close</t>
+          <t>* Valve Action : Fail Close</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       <c r="A86" s="3" t="n"/>
       <c r="B86" s="3" t="n"/>
       <c r="C86" s="3" t="n"/>
-      <c r="D86" s="3" t="n"/>
+      <c r="D86" s="4" t="n"/>
       <c r="E86" s="3" t="n"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>AIT-6002 &gt;= 17 Mohm-cm 연속 120초</t>
+          <t>AIT-5003 TOC &gt; 5 ppb 30sec</t>
         </is>
       </c>
       <c r="H86" s="3" t="n"/>
@@ -3936,7 +3936,7 @@
       <c r="A87" s="3" t="n"/>
       <c r="B87" s="3" t="n"/>
       <c r="C87" s="3" t="n"/>
-      <c r="D87" s="3" t="n"/>
+      <c r="D87" s="4" t="n"/>
       <c r="E87" s="3" t="n"/>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>PIT-6003 &gt;= 2.0 bar</t>
+          <t>E-STOP PB 동작</t>
         </is>
       </c>
       <c r="H87" s="3" t="n"/>
@@ -3957,11 +3957,31 @@
       <c r="N87" s="3" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n"/>
-      <c r="B88" s="3" t="n"/>
-      <c r="C88" s="3" t="n"/>
-      <c r="D88" s="3" t="n"/>
-      <c r="E88" s="3" t="n"/>
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>IL-5103-02</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>XV-5103</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>PERMISSIVE</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -3969,110 +3989,136 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>FAB 측 수요 신호 (DEMAND)</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="n"/>
-      <c r="I88" s="3" t="n"/>
-      <c r="J88" s="3" t="n"/>
-      <c r="K88" s="3" t="n"/>
-      <c r="L88" s="3" t="n"/>
-      <c r="M88" s="3" t="n"/>
-      <c r="N88" s="3" t="n"/>
+          <t>LIT-4003 &gt; 25 %</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>FB_XV5103_PERM</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>YI-Y01-C01-UW-LG-051</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
+          <t>* Valve Action : Fail Close</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>IL-1101A-01</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>P-1101A</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="A89" s="3" t="n"/>
+      <c r="B89" s="3" t="n"/>
+      <c r="C89" s="3" t="n"/>
+      <c r="D89" s="3" t="n"/>
+      <c r="E89" s="3" t="n"/>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>AIT-4001 &gt;= 17 Mohm-cm</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="n"/>
+      <c r="I89" s="3" t="n"/>
+      <c r="J89" s="3" t="n"/>
+      <c r="K89" s="3" t="n"/>
+      <c r="L89" s="3" t="n"/>
+      <c r="M89" s="3" t="n"/>
+      <c r="N89" s="3" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>IL-6101A-01</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>P-6101A</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>STOP</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D90" s="4" t="inlineStr">
         <is>
           <t>INTERLOCK</t>
         </is>
       </c>
-      <c r="E89" s="3" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>PIT-1002 Low Low &lt; 1.31 bar 5sec</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>LIT-4003 Low Low (10 %)</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
       </c>
-      <c r="I89" s="3" t="inlineStr">
+      <c r="I90" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J89" s="3" t="n">
+      <c r="J90" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K89" s="3" t="inlineStr">
-        <is>
-          <t>FB_P1101A_ILK</t>
-        </is>
-      </c>
-      <c r="L89" s="3" t="inlineStr">
-        <is>
-          <t>YI-Y01-C01-UW-LG-011</t>
-        </is>
-      </c>
-      <c r="M89" s="3" t="inlineStr">
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>FB_P6101A_ILK</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>YI-Y01-C01-UW-LG-061</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N89" s="3" t="inlineStr">
+      <c r="N90" s="3" t="inlineStr">
         <is>
           <t>* Valve Action : Fail Stop</t>
         </is>
       </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="n"/>
-      <c r="B90" s="3" t="n"/>
-      <c r="C90" s="3" t="n"/>
-      <c r="D90" s="4" t="n"/>
-      <c r="E90" s="3" t="n"/>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>MOTOR OVERLOAD TRIP (49)</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="n"/>
-      <c r="I90" s="3" t="n"/>
-      <c r="J90" s="3" t="n"/>
-      <c r="K90" s="3" t="n"/>
-      <c r="L90" s="3" t="n"/>
-      <c r="M90" s="3" t="n"/>
-      <c r="N90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n"/>
@@ -4087,7 +4133,7 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>E-STOP PB 동작</t>
+          <t>PIT-6003 Low Low &lt; 1.5 bar 5sec</t>
         </is>
       </c>
       <c r="H91" s="3" t="n"/>
@@ -4099,125 +4145,105 @@
       <c r="N91" s="3" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>IL-1102-01</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>XV-1102</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="A92" s="3" t="n"/>
+      <c r="B92" s="3" t="n"/>
+      <c r="C92" s="3" t="n"/>
+      <c r="D92" s="4" t="n"/>
+      <c r="E92" s="3" t="n"/>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>MOTOR OVERLOAD TRIP (49)</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="n"/>
+      <c r="I92" s="3" t="n"/>
+      <c r="J92" s="3" t="n"/>
+      <c r="K92" s="3" t="n"/>
+      <c r="L92" s="3" t="n"/>
+      <c r="M92" s="3" t="n"/>
+      <c r="N92" s="3" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>IL-6102-01</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>XV-6102</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>CLOSE</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>INTERLOCK</t>
         </is>
       </c>
-      <c r="E92" s="3" t="inlineStr">
+      <c r="E93" s="3" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="F92" s="3" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>AIT-1001 전도도 High High &gt; 88.94 uS/cm</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>AIT-6002 저항률 &lt; 17 Mohm-cm 30sec</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
         <is>
           <t>MANUAL</t>
         </is>
       </c>
-      <c r="I92" s="3" t="inlineStr">
+      <c r="I93" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J92" s="3" t="n">
+      <c r="J93" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K92" s="3" t="inlineStr">
-        <is>
-          <t>FB_XV1102_ILK</t>
-        </is>
-      </c>
-      <c r="L92" s="3" t="inlineStr">
-        <is>
-          <t>YI-Y01-C01-UW-LG-011</t>
-        </is>
-      </c>
-      <c r="M92" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N92" s="3" t="inlineStr">
-        <is>
-          <t>* Valve Action : Fail Close</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="n"/>
-      <c r="B93" s="3" t="n"/>
-      <c r="C93" s="3" t="n"/>
-      <c r="D93" s="4" t="n"/>
-      <c r="E93" s="3" t="n"/>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>TIT-1004 High High &gt; 68.84 degC</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="n"/>
-      <c r="I93" s="3" t="n"/>
-      <c r="J93" s="3" t="n"/>
-      <c r="K93" s="3" t="n"/>
-      <c r="L93" s="3" t="n"/>
-      <c r="M93" s="3" t="n"/>
-      <c r="N93" s="3" t="n"/>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>FB_XV6102_ILK</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>YI-Y01-C01-UW-LG-061</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
+          <t>POU 공급 차단. FAB 직결이라 최우선. * Valve Action : Fail Close</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>IL-7101-01</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>P-7101</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t>STOP</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t>INTERLOCK</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>OR</t>
-        </is>
-      </c>
+      <c r="A94" s="3" t="n"/>
+      <c r="B94" s="3" t="n"/>
+      <c r="C94" s="3" t="n"/>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="3" t="n"/>
       <c r="F94" s="3" t="inlineStr">
         <is>
           <t>G1</t>
@@ -4225,42 +4251,16 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>LIT-7003 Low Low &lt; 15 %</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="I94" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J94" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K94" s="3" t="inlineStr">
-        <is>
-          <t>FB_P7101_ILK</t>
-        </is>
-      </c>
-      <c r="L94" s="3" t="inlineStr">
-        <is>
-          <t>YI-Y01-C01-UW-LG-071</t>
-        </is>
-      </c>
-      <c r="M94" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N94" s="3" t="inlineStr">
-        <is>
-          <t>* Valve Action : Fail Stop</t>
-        </is>
-      </c>
+          <t>AIT-6004 TOC High High &gt; 5 ppb</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="n"/>
+      <c r="I94" s="3" t="n"/>
+      <c r="J94" s="3" t="n"/>
+      <c r="K94" s="3" t="n"/>
+      <c r="L94" s="3" t="n"/>
+      <c r="M94" s="3" t="n"/>
+      <c r="N94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n"/>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>MOTOR OVERLOAD TRIP (49)</t>
+          <t>E-STOP PB 동작</t>
         </is>
       </c>
       <c r="H95" s="3" t="n"/>
@@ -4286,6 +4286,454 @@
       <c r="M95" s="3" t="n"/>
       <c r="N95" s="3" t="n"/>
     </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>IL-6102-02</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>XV-6102</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>PERMISSIVE</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>P-6101A 운전 중</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>FB_XV6102_PERM</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>YI-Y01-C01-UW-LG-061</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
+          <t>바이패스 불가 — 품질 직결. * Valve Action : Fail Close</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n"/>
+      <c r="B97" s="3" t="n"/>
+      <c r="C97" s="3" t="n"/>
+      <c r="D97" s="3" t="n"/>
+      <c r="E97" s="3" t="n"/>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>AIT-6002 &gt;= 17 Mohm-cm 연속 120초</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="n"/>
+      <c r="I97" s="3" t="n"/>
+      <c r="J97" s="3" t="n"/>
+      <c r="K97" s="3" t="n"/>
+      <c r="L97" s="3" t="n"/>
+      <c r="M97" s="3" t="n"/>
+      <c r="N97" s="3" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="n"/>
+      <c r="B98" s="3" t="n"/>
+      <c r="C98" s="3" t="n"/>
+      <c r="D98" s="3" t="n"/>
+      <c r="E98" s="3" t="n"/>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>PIT-6003 &gt;= 2.0 bar</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="n"/>
+      <c r="I98" s="3" t="n"/>
+      <c r="J98" s="3" t="n"/>
+      <c r="K98" s="3" t="n"/>
+      <c r="L98" s="3" t="n"/>
+      <c r="M98" s="3" t="n"/>
+      <c r="N98" s="3" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n"/>
+      <c r="B99" s="3" t="n"/>
+      <c r="C99" s="3" t="n"/>
+      <c r="D99" s="3" t="n"/>
+      <c r="E99" s="3" t="n"/>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>FAB 측 수요 신호 (DEMAND)</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="n"/>
+      <c r="I99" s="3" t="n"/>
+      <c r="J99" s="3" t="n"/>
+      <c r="K99" s="3" t="n"/>
+      <c r="L99" s="3" t="n"/>
+      <c r="M99" s="3" t="n"/>
+      <c r="N99" s="3" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>IL-1101A-01</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>P-1101A</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>INTERLOCK</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>PIT-1002 Low Low &lt; 1.31 bar 5sec</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>FB_P1101A_ILK</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>YI-Y01-C01-UW-LG-011</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
+          <t>* Valve Action : Fail Stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n"/>
+      <c r="B101" s="3" t="n"/>
+      <c r="C101" s="3" t="n"/>
+      <c r="D101" s="4" t="n"/>
+      <c r="E101" s="3" t="n"/>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>MOTOR OVERLOAD TRIP (49)</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="n"/>
+      <c r="I101" s="3" t="n"/>
+      <c r="J101" s="3" t="n"/>
+      <c r="K101" s="3" t="n"/>
+      <c r="L101" s="3" t="n"/>
+      <c r="M101" s="3" t="n"/>
+      <c r="N101" s="3" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="n"/>
+      <c r="B102" s="3" t="n"/>
+      <c r="C102" s="3" t="n"/>
+      <c r="D102" s="4" t="n"/>
+      <c r="E102" s="3" t="n"/>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>E-STOP PB 동작</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="n"/>
+      <c r="I102" s="3" t="n"/>
+      <c r="J102" s="3" t="n"/>
+      <c r="K102" s="3" t="n"/>
+      <c r="L102" s="3" t="n"/>
+      <c r="M102" s="3" t="n"/>
+      <c r="N102" s="3" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>IL-1102-01</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>XV-1102</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>INTERLOCK</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>AIT-1001 전도도 High High &gt; 88.94 uS/cm</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>FB_XV1102_ILK</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>YI-Y01-C01-UW-LG-011</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
+          <t>* Valve Action : Fail Close</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="n"/>
+      <c r="B104" s="3" t="n"/>
+      <c r="C104" s="3" t="n"/>
+      <c r="D104" s="4" t="n"/>
+      <c r="E104" s="3" t="n"/>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>TIT-1004 High High &gt; 68.84 degC</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="n"/>
+      <c r="I104" s="3" t="n"/>
+      <c r="J104" s="3" t="n"/>
+      <c r="K104" s="3" t="n"/>
+      <c r="L104" s="3" t="n"/>
+      <c r="M104" s="3" t="n"/>
+      <c r="N104" s="3" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>IL-7101-01</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>P-7101</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>INTERLOCK</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>LIT-7003 Low Low &lt; 15 %</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>FB_P7101_ILK</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>YI-Y01-C01-UW-LG-071</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
+          <t>* Valve Action : Fail Stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n"/>
+      <c r="B106" s="3" t="n"/>
+      <c r="C106" s="3" t="n"/>
+      <c r="D106" s="4" t="n"/>
+      <c r="E106" s="3" t="n"/>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>MOTOR OVERLOAD TRIP (49)</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="n"/>
+      <c r="I106" s="3" t="n"/>
+      <c r="J106" s="3" t="n"/>
+      <c r="K106" s="3" t="n"/>
+      <c r="L106" s="3" t="n"/>
+      <c r="M106" s="3" t="n"/>
+      <c r="N106" s="3" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
